--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F83CF079-22FB-4924-A181-FEE40D3F131D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7351DE86-2E7E-4EF5-A4FC-A34AF833B945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -489,79 +489,79 @@
     <t>efficiency</t>
   </si>
   <si>
-    <t>g_w1143180503-765_IND-w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>g_w1143180503-765_IND-w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>g_w201845280-765_IND-w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>g_w201845280-765_IND-w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>g_w201845280-765_IND-w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>g_w201845280-765_IND-w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>g_w203673991-400_IND-w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>g_w209826798-765_IND-w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>g_w209826798-765_IND-w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>g_w209826798-765_IND-w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>g_w293597835-765_IND-w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>g_w311118424-765_IND-w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>g_w315823978-765_IND-IN684-765_IND</t>
-  </si>
-  <si>
-    <t>g_w315823978-765_IND-w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>g_w315823978-765_IND-w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>g_w331275940-765_IND-w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>g_w353914865-765_IND-IN684-765_IND</t>
-  </si>
-  <si>
-    <t>g_w353914865-765_IND-w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>g_w353914865-765_IND-w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>g_w372701897-765_IND-w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>g_w386153973-765_IND-w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>g_w420797421-765_IND-w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>g_w420797421-765_IND-w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>g_w688672711-765_IND-w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>g_w759521252-765_IND-w311118424-765_IND</t>
+    <t>g_Bhuj_IND-Vadodara_IND</t>
+  </si>
+  <si>
+    <t>g_Dharmapuri_IND-Solapur_IND</t>
+  </si>
+  <si>
+    <t>g_Fatehpur_IND-Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>g_Indore_IND-Jaipur_IND</t>
+  </si>
+  <si>
+    <t>g_Indore_IND-Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>g_Indore_IND-Vadodara_IND</t>
+  </si>
+  <si>
+    <t>g_Korba_IND-Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>g_Korba_IND-Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>g_Korba_IND-Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>g_Kurnool_IND-Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>g_Kurnool_IND-Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>g_Kurnool_IND-Wardha_IND</t>
+  </si>
+  <si>
+    <t>g_Medinipur_IND-Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>g_Moga_IND-Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>g_Phalodi_IND-Jaipur_IND</t>
+  </si>
+  <si>
+    <t>g_Phalodi_IND-Moga_IND</t>
+  </si>
+  <si>
+    <t>g_Sikandarabad_IND-Jaipur_IND</t>
+  </si>
+  <si>
+    <t>g_Sikandarabad_IND-Phalodi_IND</t>
+  </si>
+  <si>
+    <t>g_Solapur_IND-Kurnool_IND</t>
+  </si>
+  <si>
+    <t>g_Tezpur_IND-Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>g_Vadodara_IND-Wardha_IND</t>
+  </si>
+  <si>
+    <t>g_Wardha_IND-Indore_IND</t>
+  </si>
+  <si>
+    <t>g_Wardha_IND-Korba_IND</t>
+  </si>
+  <si>
+    <t>g_Wardha_IND-Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>g_Wardha_IND-Solapur_IND</t>
   </si>
   <si>
     <t>~tfm_ins-at</t>
@@ -576,7 +576,7 @@
     <t>lim_type</t>
   </si>
   <si>
-    <t>e_demand_w201845280-765_IND</t>
+    <t>e_demand_Wardha_IND</t>
   </si>
   <si>
     <t>elc_buildings,elc_transport,elc_roadtransport</t>
@@ -585,199 +585,199 @@
     <t>lo</t>
   </si>
   <si>
-    <t>e_demand_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>e_demand_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>e_demand_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>e_demand_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>e_demand_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>e_demand_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>e_demand_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>e_demand_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>e_demand_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>e_demand_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>e_demand_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>e_demand_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>e_demand_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>e_demand_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>e_demand_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>ev_battery_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>ev_battery_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>ev_battery_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>ev_battery_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>ev_battery_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>ev_battery_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>ev_battery_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>ev_battery_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>ev_battery_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>ev_battery_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>ev_battery_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>ev_battery_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>ev_battery_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>ev_battery_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>ev_battery_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>ev_battery_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w203673991-400_IND</t>
+    <t>e_demand_Indore_IND</t>
+  </si>
+  <si>
+    <t>e_demand_Solapur_IND</t>
+  </si>
+  <si>
+    <t>e_demand_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>e_demand_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>e_demand_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>e_demand_Korba_IND</t>
+  </si>
+  <si>
+    <t>e_demand_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>e_demand_Moga_IND</t>
+  </si>
+  <si>
+    <t>e_demand_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>e_demand_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_demand_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>e_demand_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>e_demand_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>e_demand_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>e_demand_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>ev_battery_Wardha_IND</t>
+  </si>
+  <si>
+    <t>ev_battery_Indore_IND</t>
+  </si>
+  <si>
+    <t>ev_battery_Solapur_IND</t>
+  </si>
+  <si>
+    <t>ev_battery_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>ev_battery_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>ev_battery_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>ev_battery_Korba_IND</t>
+  </si>
+  <si>
+    <t>ev_battery_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>ev_battery_Moga_IND</t>
+  </si>
+  <si>
+    <t>ev_battery_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>ev_battery_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>ev_battery_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>ev_battery_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>ev_battery_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>ev_battery_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>ev_battery_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Wardha_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Indore_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Solapur_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Korba_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Moga_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Wardha_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Indore_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Solapur_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Korba_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Moga_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Tezpur_IND</t>
   </si>
   <si>
     <t>elc_industry</t>
   </si>
   <si>
-    <t>h_demand_w293597835-765_IND</t>
+    <t>h_demand_Solapur_IND</t>
   </si>
   <si>
     <t>het_buildings</t>
@@ -786,40 +786,40 @@
     <t>het_industry</t>
   </si>
   <si>
-    <t>h_demand_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>h_demand_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>h_demand_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>h_demand_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>h_demand_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>h_demand_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>h_demand_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>h_demand_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>h_demand_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>h_demand_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>h_demand_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>h_demand_w369866141-765_IND</t>
+    <t>h_demand_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>h_demand_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>h_demand_Wardha_IND</t>
+  </si>
+  <si>
+    <t>h_demand_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>h_demand_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>h_demand_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>h_demand_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>h_demand_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>h_demand_Korba_IND</t>
+  </si>
+  <si>
+    <t>h_demand_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>h_demand_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>h_demand_Jaipur_IND</t>
   </si>
   <si>
     <t>~tfm_topins</t>
@@ -828,1012 +828,1012 @@
     <t>io</t>
   </si>
   <si>
-    <t>e_w201845280-765_IND</t>
+    <t>e_Wardha_IND</t>
   </si>
   <si>
     <t>IN</t>
   </si>
   <si>
-    <t>e_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>e_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>e_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>e_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>e_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>e_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>e_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>e_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>e_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>e_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>e_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>e_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>e_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>e_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>h_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>h_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>h_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>h_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>h_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>h_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>h_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>h_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>h_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>h_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>h_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>h_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>h_w369866141-765_IND</t>
+    <t>e_Indore_IND</t>
+  </si>
+  <si>
+    <t>e_Solapur_IND</t>
+  </si>
+  <si>
+    <t>e_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>e_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>e_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>e_Korba_IND</t>
+  </si>
+  <si>
+    <t>e_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>e_Moga_IND</t>
+  </si>
+  <si>
+    <t>e_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>e_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>e_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>e_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>e_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>h_Solapur_IND</t>
+  </si>
+  <si>
+    <t>h_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>h_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>h_Wardha_IND</t>
+  </si>
+  <si>
+    <t>h_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>h_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>h_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>h_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>h_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>h_Korba_IND</t>
+  </si>
+  <si>
+    <t>h_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>h_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>h_Jaipur_IND</t>
   </si>
   <si>
     <t>region</t>
   </si>
   <si>
-    <t>en_gas_ccgt_w201845280-765_IND</t>
+    <t>en_gas_ccgt_Wardha_IND</t>
   </si>
   <si>
     <t>OUT</t>
   </si>
   <si>
-    <t>en_gas_turbine_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>en_biomass_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>en_biomass_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>en_biomass_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>en_biomass_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>en_biomass_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>en_biomass_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>en_biomass_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>en_biomass_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>en_biomass_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>en_biomass_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>en_biomass_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>en_biomass_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>en_biomass_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>en_biomass_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>en_biomass_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>en_biomass_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w203673991-400_IND</t>
+    <t>en_gas_turbine_Wardha_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Wardha_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Wardha_IND</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Wardha_IND</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Wardha_IND</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Wardha_IND</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Wardha_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_Wardha_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Wardha_IND</t>
+  </si>
+  <si>
+    <t>en_biomass_Wardha_IND</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Wardha_IND</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Wardha_IND</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Wardha_IND</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Wardha_IND</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Wardha_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Wardha_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Indore_IND</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Indore_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Indore_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Indore_IND</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Indore_IND</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Indore_IND</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Indore_IND</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Indore_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_Indore_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Indore_IND</t>
+  </si>
+  <si>
+    <t>en_biomass_Indore_IND</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Indore_IND</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Indore_IND</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Indore_IND</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Indore_IND</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Indore_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Indore_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Solapur_IND</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Solapur_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Solapur_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Solapur_IND</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Solapur_IND</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Solapur_IND</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Solapur_IND</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Solapur_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_Solapur_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Solapur_IND</t>
+  </si>
+  <si>
+    <t>en_biomass_Solapur_IND</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Solapur_IND</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Solapur_IND</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Solapur_IND</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Solapur_IND</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Solapur_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Solapur_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>en_biomass_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>en_biomass_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>en_biomass_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Korba_IND</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Korba_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Korba_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Korba_IND</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Korba_IND</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Korba_IND</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Korba_IND</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Korba_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_Korba_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Korba_IND</t>
+  </si>
+  <si>
+    <t>en_biomass_Korba_IND</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Korba_IND</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Korba_IND</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Korba_IND</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Korba_IND</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Korba_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Korba_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>en_biomass_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Moga_IND</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Moga_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Moga_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Moga_IND</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Moga_IND</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Moga_IND</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Moga_IND</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Moga_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_Moga_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Moga_IND</t>
+  </si>
+  <si>
+    <t>en_biomass_Moga_IND</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Moga_IND</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Moga_IND</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Moga_IND</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Moga_IND</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Moga_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Moga_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>en_biomass_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>en_biomass_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>en_biomass_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>en_biomass_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>en_biomass_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>en_biomass_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>en_biomass_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Wardha_IND</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Wardha_IND</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Indore_IND</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Indore_IND</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Solapur_IND</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Solapur_IND</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Korba_IND</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Korba_IND</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Moga_IND</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Moga_IND</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Tezpur_IND</t>
   </si>
   <si>
     <t>ELC</t>
@@ -3387,7 +3387,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03E6B5E0-1518-4751-916C-7E6490030DB0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0D70BBB-042A-4E92-8D5B-6C1309D4562D}">
   <dimension ref="B2:AG339"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3463,13 +3463,13 @@
         <v>120</v>
       </c>
       <c r="C4">
-        <v>11.024156980014389</v>
+        <v>33.072470940043168</v>
       </c>
       <c r="D4">
-        <v>355.3</v>
+        <v>299.20000000000005</v>
       </c>
       <c r="E4">
-        <v>0.98062000000000005</v>
+        <v>0.98368</v>
       </c>
       <c r="H4" t="s">
         <v>149</v>
@@ -3537,10 +3537,10 @@
         <v>11.024156980014389</v>
       </c>
       <c r="D5">
-        <v>432.3</v>
+        <v>379.50000000000006</v>
       </c>
       <c r="E5">
-        <v>0.97641999999999995</v>
+        <v>0.97929999999999995</v>
       </c>
       <c r="H5" t="s">
         <v>152</v>
@@ -3602,13 +3602,13 @@
         <v>122</v>
       </c>
       <c r="C6">
-        <v>11.024156980014389</v>
+        <v>16.536235470021584</v>
       </c>
       <c r="D6">
-        <v>233.20000000000002</v>
+        <v>309.10000000000002</v>
       </c>
       <c r="E6">
-        <v>0.98728000000000005</v>
+        <v>0.98314000000000001</v>
       </c>
       <c r="H6" t="s">
         <v>153</v>
@@ -3670,10 +3670,10 @@
         <v>11.024156980014389</v>
       </c>
       <c r="D7">
-        <v>433.40000000000003</v>
+        <v>238.70000000000002</v>
       </c>
       <c r="E7">
-        <v>0.97636000000000001</v>
+        <v>0.98697999999999997</v>
       </c>
       <c r="H7" t="s">
         <v>154</v>
@@ -3717,13 +3717,13 @@
         <v>124</v>
       </c>
       <c r="C8">
-        <v>33.072470940043168</v>
+        <v>11.024156980014389</v>
       </c>
       <c r="D8">
-        <v>390.50000000000006</v>
+        <v>292.60000000000002</v>
       </c>
       <c r="E8">
-        <v>0.97870000000000001</v>
+        <v>0.98404000000000003</v>
       </c>
       <c r="H8" t="s">
         <v>155</v>
@@ -3767,13 +3767,13 @@
         <v>125</v>
       </c>
       <c r="C9">
-        <v>11.024156980014389</v>
+        <v>16.536235470021584</v>
       </c>
       <c r="D9">
-        <v>352</v>
+        <v>304.70000000000005</v>
       </c>
       <c r="E9">
-        <v>0.98080000000000001</v>
+        <v>0.98338000000000003</v>
       </c>
       <c r="H9" t="s">
         <v>156</v>
@@ -3817,13 +3817,13 @@
         <v>126</v>
       </c>
       <c r="C10">
-        <v>10.724858600466492</v>
+        <v>11.024156980014389</v>
       </c>
       <c r="D10">
-        <v>244.20000000000002</v>
+        <v>379.50000000000006</v>
       </c>
       <c r="E10">
-        <v>0.98668</v>
+        <v>0.97929999999999995</v>
       </c>
       <c r="H10" t="s">
         <v>157</v>
@@ -3867,13 +3867,13 @@
         <v>127</v>
       </c>
       <c r="C11">
-        <v>16.536235470021584</v>
+        <v>11.024156980014389</v>
       </c>
       <c r="D11">
-        <v>304.70000000000005</v>
+        <v>425.70000000000005</v>
       </c>
       <c r="E11">
-        <v>0.98338000000000003</v>
+        <v>0.97677999999999998</v>
       </c>
       <c r="H11" t="s">
         <v>158</v>
@@ -3920,10 +3920,10 @@
         <v>11.024156980014389</v>
       </c>
       <c r="D12">
-        <v>238.70000000000002</v>
+        <v>343.20000000000005</v>
       </c>
       <c r="E12">
-        <v>0.98697999999999997</v>
+        <v>0.98128000000000004</v>
       </c>
       <c r="H12" t="s">
         <v>159</v>
@@ -3967,13 +3967,13 @@
         <v>129</v>
       </c>
       <c r="C13">
-        <v>11.024156980014389</v>
+        <v>33.072470940043168</v>
       </c>
       <c r="D13">
-        <v>292.60000000000002</v>
+        <v>185.9</v>
       </c>
       <c r="E13">
-        <v>0.98404000000000003</v>
+        <v>0.98985999999999996</v>
       </c>
       <c r="H13" t="s">
         <v>160</v>
@@ -4020,10 +4020,10 @@
         <v>11.024156980014389</v>
       </c>
       <c r="D14">
-        <v>199.10000000000002</v>
+        <v>315.70000000000005</v>
       </c>
       <c r="E14">
-        <v>0.98914000000000002</v>
+        <v>0.98277999999999999</v>
       </c>
       <c r="H14" t="s">
         <v>161</v>
@@ -4067,13 +4067,13 @@
         <v>131</v>
       </c>
       <c r="C15">
-        <v>16.536235470021584</v>
+        <v>22.048313960028779</v>
       </c>
       <c r="D15">
-        <v>309.10000000000002</v>
+        <v>339.90000000000003</v>
       </c>
       <c r="E15">
-        <v>0.98314000000000001</v>
+        <v>0.98146</v>
       </c>
       <c r="H15" t="s">
         <v>162</v>
@@ -4117,13 +4117,13 @@
         <v>132</v>
       </c>
       <c r="C16">
-        <v>11.024156980014389</v>
+        <v>14.599109846836555</v>
       </c>
       <c r="D16">
-        <v>315.70000000000005</v>
+        <v>271.70000000000005</v>
       </c>
       <c r="E16">
-        <v>0.98277999999999999</v>
+        <v>0.98517999999999994</v>
       </c>
       <c r="H16" t="s">
         <v>163</v>
@@ -4167,13 +4167,13 @@
         <v>133</v>
       </c>
       <c r="C17">
-        <v>22.048313960028779</v>
+        <v>5.5120784900071946</v>
       </c>
       <c r="D17">
-        <v>339.90000000000003</v>
+        <v>283.8</v>
       </c>
       <c r="E17">
-        <v>0.98146</v>
+        <v>0.98451999999999995</v>
       </c>
       <c r="H17" t="s">
         <v>164</v>
@@ -4217,13 +4217,13 @@
         <v>134</v>
       </c>
       <c r="C18">
-        <v>33.072470940043168</v>
+        <v>11.024156980014389</v>
       </c>
       <c r="D18">
-        <v>185.9</v>
+        <v>355.3</v>
       </c>
       <c r="E18">
-        <v>0.98985999999999996</v>
+        <v>0.98062000000000005</v>
       </c>
       <c r="H18" t="s">
         <v>165</v>
@@ -4267,13 +4267,13 @@
         <v>135</v>
       </c>
       <c r="C19">
-        <v>5.5120784900071946</v>
+        <v>11.024156980014389</v>
       </c>
       <c r="D19">
-        <v>282.70000000000005</v>
+        <v>432.3</v>
       </c>
       <c r="E19">
-        <v>0.98458000000000001</v>
+        <v>0.97641999999999995</v>
       </c>
       <c r="H19" t="s">
         <v>166</v>
@@ -4320,10 +4320,10 @@
         <v>11.024156980014389</v>
       </c>
       <c r="D20">
-        <v>425.70000000000005</v>
+        <v>190.3</v>
       </c>
       <c r="E20">
-        <v>0.97677999999999998</v>
+        <v>0.98961999999999994</v>
       </c>
       <c r="H20" t="s">
         <v>167</v>
@@ -4370,10 +4370,10 @@
         <v>11.024156980014389</v>
       </c>
       <c r="D21">
-        <v>379.50000000000006</v>
+        <v>264</v>
       </c>
       <c r="E21">
-        <v>0.97929999999999995</v>
+        <v>0.98560000000000003</v>
       </c>
       <c r="H21" t="s">
         <v>168</v>
@@ -4420,10 +4420,10 @@
         <v>11.024156980014389</v>
       </c>
       <c r="D22">
-        <v>343.20000000000005</v>
+        <v>199.10000000000002</v>
       </c>
       <c r="E22">
-        <v>0.98128000000000004</v>
+        <v>0.98914000000000002</v>
       </c>
       <c r="H22" t="s">
         <v>169</v>
@@ -4467,13 +4467,13 @@
         <v>139</v>
       </c>
       <c r="C23">
-        <v>5.5120784900071946</v>
+        <v>10.724858600466492</v>
       </c>
       <c r="D23">
-        <v>283.8</v>
+        <v>244.20000000000002</v>
       </c>
       <c r="E23">
-        <v>0.98451999999999995</v>
+        <v>0.98668</v>
       </c>
       <c r="H23" t="s">
         <v>170</v>
@@ -4517,13 +4517,13 @@
         <v>140</v>
       </c>
       <c r="C24">
-        <v>11.024156980014389</v>
+        <v>5.5120784900071946</v>
       </c>
       <c r="D24">
-        <v>379.50000000000006</v>
+        <v>282.70000000000005</v>
       </c>
       <c r="E24">
-        <v>0.97929999999999995</v>
+        <v>0.98458000000000001</v>
       </c>
       <c r="H24" t="s">
         <v>171</v>
@@ -4570,10 +4570,10 @@
         <v>11.024156980014389</v>
       </c>
       <c r="D25">
-        <v>264</v>
+        <v>233.20000000000002</v>
       </c>
       <c r="E25">
-        <v>0.98560000000000003</v>
+        <v>0.98728000000000005</v>
       </c>
       <c r="H25" t="s">
         <v>172</v>
@@ -4617,13 +4617,13 @@
         <v>142</v>
       </c>
       <c r="C26">
-        <v>11.024156980014389</v>
+        <v>33.072470940043168</v>
       </c>
       <c r="D26">
-        <v>190.3</v>
+        <v>390.50000000000006</v>
       </c>
       <c r="E26">
-        <v>0.98961999999999994</v>
+        <v>0.97870000000000001</v>
       </c>
       <c r="H26" t="s">
         <v>173</v>
@@ -4667,13 +4667,13 @@
         <v>143</v>
       </c>
       <c r="C27">
-        <v>33.072470940043168</v>
+        <v>11.024156980014389</v>
       </c>
       <c r="D27">
-        <v>299.20000000000005</v>
+        <v>352</v>
       </c>
       <c r="E27">
-        <v>0.98368</v>
+        <v>0.98080000000000001</v>
       </c>
       <c r="H27" t="s">
         <v>174</v>
@@ -4717,13 +4717,13 @@
         <v>144</v>
       </c>
       <c r="C28">
-        <v>14.599109846836555</v>
+        <v>11.024156980014389</v>
       </c>
       <c r="D28">
-        <v>271.70000000000005</v>
+        <v>433.40000000000003</v>
       </c>
       <c r="E28">
-        <v>0.98517999999999994</v>
+        <v>0.97636000000000001</v>
       </c>
       <c r="H28" t="s">
         <v>175</v>
@@ -11525,7 +11525,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2B8CD0C-B79A-4008-BD42-FB5E397177D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D467F3CB-E046-4FC6-B138-6CBB2976CED2}">
   <dimension ref="B9:L20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -22960,7 +22960,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D991129-B2BA-464C-A207-A750F9C0DFFC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F61819CB-CB5C-4039-A527-41429AA899DF}">
   <dimension ref="A1:I173"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D40D94A-82F6-4784-8253-57A18F1FB164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03629DEF-6D65-4754-9453-CF41EAB6E4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3467,7 +3467,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D17CB739-AD0A-42A7-9FC0-58DDC5F07B16}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F731092B-7ADA-41A9-941E-986BF6E0D6C1}">
   <dimension ref="B2:AG419"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -14030,7 +14030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176BE1FF-8346-4A5D-B7BD-1AB376742E0B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0A75E99-14C1-4E9F-A84A-0DC185B067D0}">
   <dimension ref="B9:L20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -25247,7 +25247,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0FCAB12-791D-4F2F-A73A-8DABF49C7D26}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC2906BC-E47F-4B11-A589-A74290670C0B}">
   <dimension ref="A1:I173"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
